--- a/test_calcs.xlsx
+++ b/test_calcs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="8_{C7C7E276-6A03-F043-BD40-304A7890F963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37612356-E9D2-E044-851B-D31022639BA0}"/>
   <bookViews>
-    <workbookView xWindow="30400" yWindow="660" windowWidth="38080" windowHeight="20780" xr2:uid="{77C8FE66-F471-6F4F-880B-A0D9347144D5}"/>
+    <workbookView minimized="1" xWindow="30400" yWindow="660" windowWidth="38080" windowHeight="19100" xr2:uid="{77C8FE66-F471-6F4F-880B-A0D9347144D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/test_calcs.xlsx
+++ b/test_calcs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="30" documentId="8_{C7C7E276-6A03-F043-BD40-304A7890F963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37612356-E9D2-E044-851B-D31022639BA0}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="30400" yWindow="660" windowWidth="38080" windowHeight="19100" xr2:uid="{77C8FE66-F471-6F4F-880B-A0D9347144D5}"/>
+    <workbookView minimized="1" xWindow="160" yWindow="760" windowWidth="29920" windowHeight="17480" xr2:uid="{77C8FE66-F471-6F4F-880B-A0D9347144D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
